--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2020_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2020_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:45</t>
+    <t xml:space="preserve">2026-09-09 22:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2020_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2020_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:33</t>
+    <t xml:space="preserve">2026-09-12 19:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2020_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2020_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:49</t>
+    <t xml:space="preserve">2026-09-24 00:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2020_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2020_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:27</t>
+    <t xml:space="preserve">2026-09-27 23:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -592,7 +592,7 @@
         <v>2020</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>19.43</v>
+        <v>194.3</v>
       </c>
     </row>
     <row r="3">
@@ -609,7 +609,7 @@
         <v>2020</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>10.54</v>
+        <v>105.36</v>
       </c>
     </row>
     <row r="4">
@@ -626,7 +626,7 @@
         <v>2020</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>9.42</v>
+        <v>94.17</v>
       </c>
     </row>
     <row r="5">
@@ -643,7 +643,7 @@
         <v>2020</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>7.06</v>
+        <v>70.62</v>
       </c>
     </row>
     <row r="6">
@@ -660,7 +660,7 @@
         <v>2020</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>5.54</v>
+        <v>55.43</v>
       </c>
     </row>
     <row r="7">
@@ -677,7 +677,7 @@
         <v>2020</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>5.1</v>
+        <v>51.04</v>
       </c>
     </row>
     <row r="8">
@@ -694,7 +694,7 @@
         <v>2020</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>4.46</v>
+        <v>44.57</v>
       </c>
     </row>
     <row r="9">
@@ -711,7 +711,7 @@
         <v>2020</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>4.26</v>
+        <v>42.64</v>
       </c>
     </row>
     <row r="10">
@@ -728,7 +728,7 @@
         <v>2020</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>3.59</v>
+        <v>35.86</v>
       </c>
     </row>
     <row r="11">
@@ -745,7 +745,7 @@
         <v>2020</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>3.02</v>
+        <v>30.17</v>
       </c>
     </row>
     <row r="12">
@@ -762,7 +762,7 @@
         <v>2020</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>2.47</v>
+        <v>24.66</v>
       </c>
     </row>
     <row r="13">
@@ -779,7 +779,7 @@
         <v>2020</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>2.36</v>
+        <v>23.64</v>
       </c>
     </row>
     <row r="14">
@@ -796,7 +796,7 @@
         <v>2020</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1.99</v>
+        <v>19.91</v>
       </c>
     </row>
     <row r="15">
@@ -813,7 +813,7 @@
         <v>2020</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1.29</v>
+        <v>12.88</v>
       </c>
     </row>
     <row r="16">
@@ -830,7 +830,7 @@
         <v>2020</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.85</v>
+        <v>8.45</v>
       </c>
     </row>
     <row r="17">
@@ -847,7 +847,7 @@
         <v>2020</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.66</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="18">
@@ -864,7 +864,7 @@
         <v>2020</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.51</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="19">
@@ -881,7 +881,7 @@
         <v>2020</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.44</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="20">
@@ -898,7 +898,7 @@
         <v>2020</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.3</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="21">
@@ -915,7 +915,7 @@
         <v>2020</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.11</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="22">
@@ -932,7 +932,7 @@
         <v>2020</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.09</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="23">
@@ -949,7 +949,7 @@
         <v>2020</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.05</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="24">
@@ -966,7 +966,7 @@
         <v>2020</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="25">
@@ -983,7 +983,7 @@
         <v>2020</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>-0.11</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="26">
@@ -1000,7 +1000,7 @@
         <v>2020</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-0.2</v>
+        <v>-2.02</v>
       </c>
     </row>
     <row r="27">
@@ -1017,7 +1017,7 @@
         <v>2020</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>-0.2</v>
+        <v>-2.03</v>
       </c>
     </row>
     <row r="28">
@@ -1034,7 +1034,7 @@
         <v>2020</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>-0.38</v>
+        <v>-3.75</v>
       </c>
     </row>
     <row r="29">
@@ -1051,7 +1051,7 @@
         <v>2020</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>-0.42</v>
+        <v>-4.15</v>
       </c>
     </row>
     <row r="30">
@@ -1068,7 +1068,7 @@
         <v>2020</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>-0.45</v>
+        <v>-4.5</v>
       </c>
     </row>
     <row r="31">
@@ -1085,7 +1085,7 @@
         <v>2020</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>-0.45</v>
+        <v>-4.5</v>
       </c>
     </row>
     <row r="32">
@@ -1102,7 +1102,7 @@
         <v>2020</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>-0.75</v>
+        <v>-7.52</v>
       </c>
     </row>
     <row r="33">
@@ -1119,7 +1119,7 @@
         <v>2020</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>-0.78</v>
+        <v>-7.79</v>
       </c>
     </row>
     <row r="34">
@@ -1136,7 +1136,7 @@
         <v>2020</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>-0.9</v>
+        <v>-9.01</v>
       </c>
     </row>
     <row r="35">
@@ -1153,7 +1153,7 @@
         <v>2020</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>-1.19</v>
+        <v>-11.89</v>
       </c>
     </row>
     <row r="36">
@@ -1170,7 +1170,7 @@
         <v>2020</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>-1.41</v>
+        <v>-14.11</v>
       </c>
     </row>
     <row r="37">
@@ -1187,7 +1187,7 @@
         <v>2020</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>-1.89</v>
+        <v>-18.9</v>
       </c>
     </row>
     <row r="38">
@@ -1204,7 +1204,7 @@
         <v>2020</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>-2.27</v>
+        <v>-22.67</v>
       </c>
     </row>
     <row r="39">
@@ -1221,7 +1221,7 @@
         <v>2020</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>-2.78</v>
+        <v>-27.78</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2020_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2020_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:10</t>
+    <t xml:space="preserve">2026-10-01 20:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2020_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2020_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:56</t>
+    <t xml:space="preserve">2026-10-02 13:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2020_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2020_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:26</t>
+    <t xml:space="preserve">2026-10-04 08:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2020_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2020_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:14</t>
+    <t xml:space="preserve">2026-10-05 08:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
